--- a/history_matching/example/iter1/Cuts/RadiusShouldBe15/test_data.xlsx
+++ b/history_matching/example/iter1/Cuts/RadiusShouldBe15/test_data.xlsx
@@ -2,6 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
     <workbookView activeTab="0"/>
   </bookViews>
@@ -14,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="33">
   <si>
     <t>Sample_Id</t>
   </si>
@@ -67,43 +68,52 @@
     <t>Z_Noiseless</t>
   </si>
   <si>
-    <t>Data_20170712_102507.000031</t>
-  </si>
-  <si>
-    <t>Data_20170712_102507</t>
-  </si>
-  <si>
-    <t>Data_20170712_102507.000032</t>
-  </si>
-  <si>
-    <t>Data_20170712_102507.000033</t>
-  </si>
-  <si>
-    <t>Data_20170712_102507.000034</t>
-  </si>
-  <si>
-    <t>Data_20170712_102507.000035</t>
-  </si>
-  <si>
-    <t>Data_20170712_102507.000036</t>
-  </si>
-  <si>
-    <t>Data_20170712_102507.000037</t>
-  </si>
-  <si>
-    <t>Data_20170712_102507.000038</t>
-  </si>
-  <si>
-    <t>Data_20170712_102507.000039</t>
-  </si>
-  <si>
-    <t>Data_20170712_102507.000040</t>
-  </si>
-  <si>
-    <t>Data_20170712_102507.000041</t>
-  </si>
-  <si>
-    <t>Data_20170712_102507.000042</t>
+    <t>Data_20180119_074303.000043</t>
+  </si>
+  <si>
+    <t>Data_20180119_074303</t>
+  </si>
+  <si>
+    <t>Data_20180119_074303.000044</t>
+  </si>
+  <si>
+    <t>Data_20180119_074303.000045</t>
+  </si>
+  <si>
+    <t>Data_20180119_074303.000046</t>
+  </si>
+  <si>
+    <t>Data_20180119_074303.000047</t>
+  </si>
+  <si>
+    <t>Data_20180119_074303.000048</t>
+  </si>
+  <si>
+    <t>Data_20180119_074303.000049</t>
+  </si>
+  <si>
+    <t>Data_20180119_074303.000050</t>
+  </si>
+  <si>
+    <t>Data_20180119_074303.000051</t>
+  </si>
+  <si>
+    <t>Data_20180119_074303.000052</t>
+  </si>
+  <si>
+    <t>Data_20180119_074303.000053</t>
+  </si>
+  <si>
+    <t>Data_20180119_074303.000054</t>
+  </si>
+  <si>
+    <t>Data_20180119_074303.000055</t>
+  </si>
+  <si>
+    <t>Data_20180119_074303.000056</t>
+  </si>
+  <si>
+    <t>Data_20180119_074303.000057</t>
   </si>
 </sst>
 </file>
@@ -452,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q13"/>
+  <dimension ref="A1:Q16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:17">
@@ -513,52 +523,52 @@
         <v>17</v>
       </c>
       <c r="B2" s="1" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="C2" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="D2" t="n">
-        <v>-7.898153762611877</v>
+        <v>-4.229400398706723</v>
       </c>
       <c r="E2" t="n">
-        <v>-11.98075745092109</v>
+        <v>12.59799188807671</v>
       </c>
       <c r="F2" t="s">
         <v>18</v>
       </c>
       <c r="G2" t="n">
-        <v>13.60069921258569</v>
+        <v>13.01920971413401</v>
       </c>
       <c r="H2" t="n">
-        <v>13.65981265389112</v>
+        <v>11.56006161295454</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.05911344130543306</v>
+        <v>1.459148101179469</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001010246206106678</v>
+        <v>-1.606865949165527e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>13.66082290009723</v>
+        <v>11.56006159688588</v>
       </c>
       <c r="L2" t="n">
-        <v>2.932927553971431</v>
+        <v>3.933822174127514</v>
       </c>
       <c r="M2" t="n">
-        <v>0.07901441305875778</v>
+        <v>1.020723723023195e-07</v>
       </c>
       <c r="N2" t="n">
-        <v>0.58823443593755</v>
+        <v>1.383318451573712</v>
       </c>
       <c r="O2" t="b">
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.0264093699126158</v>
+        <v>0.5867740283782682</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.03939667032252793</v>
+        <v>0.972765389433759</v>
       </c>
     </row>
     <row r="3" spans="1:17">
@@ -566,52 +576,52 @@
         <v>19</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="C3" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="D3" t="n">
-        <v>-24.52284498465529</v>
+        <v>-7.585525158281533</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.979899562656556</v>
+        <v>-11.14638854582135</v>
       </c>
       <c r="F3" t="s">
         <v>18</v>
       </c>
       <c r="G3" t="n">
-        <v>25.73617123929208</v>
+        <v>13.94611407327717</v>
       </c>
       <c r="H3" t="n">
-        <v>23.21019170102676</v>
+        <v>12.20630841657322</v>
       </c>
       <c r="I3" t="n">
-        <v>2.525979538265322</v>
+        <v>1.739805656703949</v>
       </c>
       <c r="J3" t="n">
-        <v>0.006566042434146793</v>
+        <v>4.593453054592234e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>23.21675774346091</v>
+        <v>12.20630842116667</v>
       </c>
       <c r="L3" t="n">
-        <v>2.956924385671374</v>
+        <v>3.933822174127514</v>
       </c>
       <c r="M3" t="n">
-        <v>0.10301124304533</v>
+        <v>1.020723719669408e-07</v>
       </c>
       <c r="N3" t="n">
-        <v>3.600889938146703</v>
+        <v>1.123440206228027</v>
       </c>
       <c r="O3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.104101032355408</v>
+        <v>0.699636150036272</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.642432181035002</v>
+        <v>1.159870408431281</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -619,52 +629,52 @@
         <v>20</v>
       </c>
       <c r="B4" s="1" t="n">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="C4" t="n">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D4" t="n">
-        <v>4.177455311109782</v>
+        <v>6.936342233167339</v>
       </c>
       <c r="E4" t="n">
-        <v>13.73693115827579</v>
+        <v>30.45356584416535</v>
       </c>
       <c r="F4" t="s">
         <v>18</v>
       </c>
       <c r="G4" t="n">
-        <v>13.9392281146264</v>
+        <v>30.50067662057578</v>
       </c>
       <c r="H4" t="n">
-        <v>13.9185159162646</v>
+        <v>31.09906353441829</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02071219836180482</v>
+        <v>-0.5983869138425106</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.003595422612416312</v>
+        <v>-4.748733498263497e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>13.91492049365218</v>
+        <v>31.09906348693096</v>
       </c>
       <c r="L4" t="n">
-        <v>2.934058065287674</v>
+        <v>3.933822174127527</v>
       </c>
       <c r="M4" t="n">
-        <v>0.08014491945505142</v>
+        <v>1.02072385185016e-07</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4765699257915901</v>
+        <v>6.473991381464103</v>
       </c>
       <c r="O4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01067597448489788</v>
+        <v>-0.2406320975570746</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.01592395749469223</v>
+        <v>-0.3989245685214089</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -672,52 +682,52 @@
         <v>21</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="C5" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D5" t="n">
-        <v>6.353546242975462</v>
+        <v>-27.36270515855208</v>
       </c>
       <c r="E5" t="n">
-        <v>-16.18135742091141</v>
+        <v>3.820391673025171</v>
       </c>
       <c r="F5" t="s">
         <v>18</v>
       </c>
       <c r="G5" t="n">
-        <v>17.32206093675309</v>
+        <v>25.30611127848498</v>
       </c>
       <c r="H5" t="n">
-        <v>16.9675634758367</v>
+        <v>30.326175094186</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3544974609163916</v>
+        <v>-5.020063815701018</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.003555728202833542</v>
+        <v>2.841505215148759e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>16.96400774763386</v>
+        <v>30.32617512260105</v>
       </c>
       <c r="L5" t="n">
-        <v>2.93905862119275</v>
+        <v>3.933822174127546</v>
       </c>
       <c r="M5" t="n">
-        <v>0.08514548093080521</v>
+        <v>1.020724043898662e-07</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8621819135222811</v>
+        <v>6.163186183784885</v>
       </c>
       <c r="O5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1571821618878454</v>
+        <v>-2.018741654605559</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.2343098699815189</v>
+        <v>-3.346709153498125</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -725,52 +735,52 @@
         <v>22</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="C6" t="n">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="D6" t="n">
-        <v>5.207803852178216</v>
+        <v>12.21262988442415</v>
       </c>
       <c r="E6" t="n">
-        <v>17.0070014045056</v>
+        <v>14.33645310392244</v>
       </c>
       <c r="F6" t="s">
         <v>18</v>
       </c>
       <c r="G6" t="n">
-        <v>17.77995294400602</v>
+        <v>17.8705885412703</v>
       </c>
       <c r="H6" t="n">
-        <v>17.28870039370537</v>
+        <v>15.91254321909321</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4912525503006506</v>
+        <v>1.958045322177092</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.003928732170221529</v>
+        <v>-3.809754194518729e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>17.28477166153515</v>
+        <v>15.91254318099567</v>
       </c>
       <c r="L6" t="n">
-        <v>2.936959568386891</v>
+        <v>3.933822174127525</v>
       </c>
       <c r="M6" t="n">
-        <v>0.08304642885923386</v>
+        <v>1.020723836293899e-07</v>
       </c>
       <c r="N6" t="n">
-        <v>1.003197340399202</v>
+        <v>0.3669652395479821</v>
       </c>
       <c r="O6" t="b">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2174241539990341</v>
+        <v>0.7873979003327921</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.3241921650796563</v>
+        <v>1.305363543907185</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -778,52 +788,52 @@
         <v>23</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="C7" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="D7" t="n">
-        <v>14.45776138904563</v>
+        <v>-3.039800158258757</v>
       </c>
       <c r="E7" t="n">
-        <v>18.46544097256609</v>
+        <v>11.3299682663736</v>
       </c>
       <c r="F7" t="s">
         <v>18</v>
       </c>
       <c r="G7" t="n">
-        <v>24.7927828253155</v>
+        <v>10.53955641694504</v>
       </c>
       <c r="H7" t="n">
-        <v>24.58121368505618</v>
+        <v>10.50607300553116</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2115691402593143</v>
+        <v>0.03348341141387579</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.005878377098220729</v>
+        <v>-2.281073781467178e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>24.57533530795796</v>
+        <v>10.50607298272043</v>
       </c>
       <c r="L7" t="n">
-        <v>2.951837595013093</v>
+        <v>3.933822174127514</v>
       </c>
       <c r="M7" t="n">
-        <v>0.09792445600032806</v>
+        <v>1.020723722956527e-07</v>
       </c>
       <c r="N7" t="n">
-        <v>4.198320566287197</v>
+        <v>1.807163801945037</v>
       </c>
       <c r="O7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0.09534020009215925</v>
+        <v>0.01346484935399776</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.1419097962359926</v>
+        <v>0.0223222889767451</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -831,52 +841,52 @@
         <v>24</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="C8" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9723046034035718</v>
+        <v>-22.38024991159007</v>
       </c>
       <c r="E8" t="n">
-        <v>-14.03956635398707</v>
+        <v>-8.290482612828129</v>
       </c>
       <c r="F8" t="s">
         <v>18</v>
       </c>
       <c r="G8" t="n">
-        <v>14.47227201195521</v>
+        <v>24.21779708941035</v>
       </c>
       <c r="H8" t="n">
-        <v>13.82417246888241</v>
+        <v>24.21197113881453</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6480995430728012</v>
+        <v>0.00582595059581692</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.002043736431486367</v>
+        <v>4.096687647249113e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>13.82212873245092</v>
+        <v>24.21197117978141</v>
       </c>
       <c r="L8" t="n">
-        <v>2.933275593824258</v>
+        <v>3.933822174127535</v>
       </c>
       <c r="M8" t="n">
-        <v>0.07936245203018188</v>
+        <v>1.020723928693991e-07</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5173633707992099</v>
+        <v>3.704452875324964</v>
       </c>
       <c r="O8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2855662820324094</v>
+        <v>0.002342800173286983</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.4259813217031503</v>
+        <v>0.003883939664527573</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -884,52 +894,52 @@
         <v>25</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C9" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D9" t="n">
-        <v>-13.63797246068165</v>
+        <v>-14.7553421001751</v>
       </c>
       <c r="E9" t="n">
-        <v>-19.26519083757022</v>
+        <v>21.73706300018365</v>
       </c>
       <c r="F9" t="s">
         <v>18</v>
       </c>
       <c r="G9" t="n">
-        <v>22.44277302469148</v>
+        <v>27.71241254236175</v>
       </c>
       <c r="H9" t="n">
-        <v>24.09909614444669</v>
+        <v>25.7639143853562</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.656323119755211</v>
+        <v>1.948498157005549</v>
       </c>
       <c r="J9" t="n">
-        <v>0.003154486127529621</v>
+        <v>3.650826370083708e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>24.10225063057422</v>
+        <v>25.76391442186447</v>
       </c>
       <c r="L9" t="n">
-        <v>2.943519415054729</v>
+        <v>3.933822174127522</v>
       </c>
       <c r="M9" t="n">
-        <v>0.08960627019405365</v>
+        <v>1.020723808329485e-07</v>
       </c>
       <c r="N9" t="n">
-        <v>3.994090580886169</v>
+        <v>4.328543039446838</v>
       </c>
       <c r="O9" t="b">
         <v>1</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.7281829674722591</v>
+        <v>0.7835586243348122</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.084925739789321</v>
+        <v>1.298998717533325</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -937,52 +947,52 @@
         <v>26</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="C10" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D10" t="n">
-        <v>2.772618375806935</v>
+        <v>14.09060319255523</v>
       </c>
       <c r="E10" t="n">
-        <v>9.375532043181707</v>
+        <v>8.945564849255105</v>
       </c>
       <c r="F10" t="s">
         <v>18</v>
       </c>
       <c r="G10" t="n">
-        <v>9.85452438844805</v>
+        <v>17.92754175575471</v>
       </c>
       <c r="H10" t="n">
-        <v>10.53534309205907</v>
+        <v>14.24639036530311</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.6808187036110152</v>
+        <v>3.681151390451596</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.003107573931566952</v>
+        <v>-3.116574066839883e-08</v>
       </c>
       <c r="K10" t="n">
-        <v>10.5322355181275</v>
+        <v>14.24639033413737</v>
       </c>
       <c r="L10" t="n">
-        <v>2.931018731812546</v>
+        <v>3.933822174127526</v>
       </c>
       <c r="M10" t="n">
-        <v>0.07710558921098709</v>
+        <v>1.020723843209679e-07</v>
       </c>
       <c r="N10" t="n">
-        <v>1.962830012866281</v>
+        <v>0.3030525648739315</v>
       </c>
       <c r="O10" t="b">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.2977398989551961</v>
+        <v>1.480318566155187</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.4442593362646144</v>
+        <v>2.45410089207913</v>
       </c>
     </row>
     <row r="11" spans="1:17">
@@ -990,52 +1000,52 @@
         <v>27</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C11" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="D11" t="n">
-        <v>10.43538390339322</v>
+        <v>-6.06715556140871</v>
       </c>
       <c r="E11" t="n">
-        <v>-17.25558377923974</v>
+        <v>18.08121041562056</v>
       </c>
       <c r="F11" t="s">
         <v>18</v>
       </c>
       <c r="G11" t="n">
-        <v>20.83286703553734</v>
+        <v>19.85064731528694</v>
       </c>
       <c r="H11" t="n">
-        <v>19.98475966556973</v>
+        <v>16.38898631145719</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8481073699676145</v>
+        <v>3.46166100382975</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.004477646520270421</v>
+        <v>-5.234419406425958e-09</v>
       </c>
       <c r="K11" t="n">
-        <v>19.98028201904945</v>
+        <v>16.38898630622277</v>
       </c>
       <c r="L11" t="n">
-        <v>2.945411182593556</v>
+        <v>3.933822174127516</v>
       </c>
       <c r="M11" t="n">
-        <v>0.09149803966283798</v>
+        <v>1.02072373665625e-07</v>
       </c>
       <c r="N11" t="n">
-        <v>2.184962430704738</v>
+        <v>0.5585595325316726</v>
       </c>
       <c r="O11" t="b">
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>0.3740483416164776</v>
+        <v>1.392053864277546</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.5571739236106618</v>
+        <v>2.307773953696121</v>
       </c>
     </row>
     <row r="12" spans="1:17">
@@ -1043,52 +1053,52 @@
         <v>28</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="C12" t="n">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="D12" t="n">
-        <v>11.0538195331335</v>
+        <v>14.28903032719646</v>
       </c>
       <c r="E12" t="n">
-        <v>-13.63172191462643</v>
+        <v>-20.46054638787901</v>
       </c>
       <c r="F12" t="s">
         <v>18</v>
       </c>
       <c r="G12" t="n">
-        <v>18.65798726313595</v>
+        <v>24.28244070015385</v>
       </c>
       <c r="H12" t="n">
-        <v>16.99407592570111</v>
+        <v>23.68023017063854</v>
       </c>
       <c r="I12" t="n">
-        <v>1.66391133743484</v>
+        <v>0.6022105295153111</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.00471474213824674</v>
+        <v>-2.847280959715621e-08</v>
       </c>
       <c r="K12" t="n">
-        <v>16.98936118356286</v>
+        <v>23.68023014216573</v>
       </c>
       <c r="L12" t="n">
-        <v>2.944032250816217</v>
+        <v>3.933822174127526</v>
       </c>
       <c r="M12" t="n">
-        <v>0.09011910855770111</v>
+        <v>1.020723847240769e-07</v>
       </c>
       <c r="N12" t="n">
-        <v>0.8728936190575716</v>
+        <v>3.490621375282168</v>
       </c>
       <c r="O12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P12" t="n">
-        <v>0.7321611929935264</v>
+        <v>0.2421697364822928</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.090787260939876</v>
+        <v>0.4014736962188845</v>
       </c>
     </row>
     <row r="13" spans="1:17">
@@ -1096,52 +1106,211 @@
         <v>29</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="C13" t="n">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.066511104759158</v>
+        <v>10.40118487897376</v>
       </c>
       <c r="E13" t="n">
-        <v>24.54768424160156</v>
+        <v>-4.490369908150996</v>
       </c>
       <c r="F13" t="s">
         <v>18</v>
       </c>
       <c r="G13" t="n">
-        <v>23.987259613998</v>
+        <v>12.74085632351055</v>
       </c>
       <c r="H13" t="n">
-        <v>25.44653450491819</v>
+        <v>10.49932625987924</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.459274890920192</v>
+        <v>2.241530063631311</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.001739845879127895</v>
+        <v>-4.366677974864336e-08</v>
       </c>
       <c r="K13" t="n">
-        <v>25.44479465903906</v>
+        <v>10.49932621621246</v>
       </c>
       <c r="L13" t="n">
-        <v>2.939468520841231</v>
+        <v>3.933822174127521</v>
       </c>
       <c r="M13" t="n">
-        <v>0.08555538207292557</v>
+        <v>1.020723791063225e-07</v>
       </c>
       <c r="N13" t="n">
-        <v>4.584990766332056</v>
+        <v>1.809876910583982</v>
       </c>
       <c r="O13" t="b">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.9013969419848895</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.494353370969349</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17">
+      <c r="A14" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="C14" t="n">
+        <v>55</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-1.763308357209354</v>
+      </c>
+      <c r="E14" t="n">
+        <v>7.087722916941972</v>
+      </c>
+      <c r="F14" t="s">
+        <v>18</v>
+      </c>
+      <c r="G14" t="n">
+        <v>8.315943902467318</v>
+      </c>
+      <c r="H14" t="n">
+        <v>8.355542835776816</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-0.03959893330949882</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-2.954971342310909e-08</v>
+      </c>
+      <c r="K14" t="n">
+        <v>8.355542806227103</v>
+      </c>
+      <c r="L14" t="n">
+        <v>3.933822174127514</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.02072371944023e-07</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2.671966517922796</v>
+      </c>
+      <c r="O14" t="b">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-0.01592409160100447</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>-0.02639926857438204</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17">
+      <c r="A15" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>56</v>
+      </c>
+      <c r="C15" t="n">
+        <v>56</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.318304742319043</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-2.198897941952368</v>
+      </c>
+      <c r="F15" t="s">
+        <v>18</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.4583320779332982</v>
+      </c>
+      <c r="H15" t="n">
+        <v>7.17886772251444</v>
+      </c>
+      <c r="I15" t="n">
+        <v>-6.720535644581141</v>
+      </c>
+      <c r="J15" t="n">
+        <v>-3.863229808747086e-08</v>
+      </c>
+      <c r="K15" t="n">
+        <v>7.178867683882141</v>
+      </c>
+      <c r="L15" t="n">
+        <v>3.933822174127514</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.020723721440128e-07</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3.14514836524134</v>
+      </c>
+      <c r="O15" t="b">
         <v>1</v>
       </c>
-      <c r="P13" t="n">
-        <v>-0.6398196366010201</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>-0.9537266750789839</v>
+      <c r="P15" t="n">
+        <v>-2.702560284146675</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>-4.480356969005749</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17">
+      <c r="A16" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>57</v>
+      </c>
+      <c r="C16" t="n">
+        <v>57</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-8.177937969688578</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-21.85798934431147</v>
+      </c>
+      <c r="F16" t="s">
+        <v>18</v>
+      </c>
+      <c r="G16" t="n">
+        <v>23.56727048122157</v>
+      </c>
+      <c r="H16" t="n">
+        <v>21.52751171232399</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.039758768897585</v>
+      </c>
+      <c r="J16" t="n">
+        <v>8.105074131498886e-09</v>
+      </c>
+      <c r="K16" t="n">
+        <v>21.52751172042906</v>
+      </c>
+      <c r="L16" t="n">
+        <v>3.933822174127517</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.020723751373223e-07</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.624938690052942</v>
+      </c>
+      <c r="O16" t="b">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.8202576906635963</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.359839143016782</v>
       </c>
     </row>
   </sheetData>

--- a/history_matching/example/iter1/Cuts/RadiusShouldBe15/test_data.xlsx
+++ b/history_matching/example/iter1/Cuts/RadiusShouldBe15/test_data.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="34">
   <si>
     <t>Sample_Id</t>
   </si>
@@ -68,52 +68,55 @@
     <t>Z_Noiseless</t>
   </si>
   <si>
-    <t>Data_20180119_074303.000043</t>
-  </si>
-  <si>
-    <t>Data_20180119_074303</t>
-  </si>
-  <si>
-    <t>Data_20180119_074303.000044</t>
-  </si>
-  <si>
-    <t>Data_20180119_074303.000045</t>
-  </si>
-  <si>
-    <t>Data_20180119_074303.000046</t>
-  </si>
-  <si>
-    <t>Data_20180119_074303.000047</t>
-  </si>
-  <si>
-    <t>Data_20180119_074303.000048</t>
-  </si>
-  <si>
-    <t>Data_20180119_074303.000049</t>
-  </si>
-  <si>
-    <t>Data_20180119_074303.000050</t>
-  </si>
-  <si>
-    <t>Data_20180119_074303.000051</t>
-  </si>
-  <si>
-    <t>Data_20180119_074303.000052</t>
-  </si>
-  <si>
-    <t>Data_20180119_074303.000053</t>
-  </si>
-  <si>
-    <t>Data_20180119_074303.000054</t>
-  </si>
-  <si>
-    <t>Data_20180119_074303.000055</t>
-  </si>
-  <si>
-    <t>Data_20180119_074303.000056</t>
-  </si>
-  <si>
-    <t>Data_20180119_074303.000057</t>
+    <t>Data_20180120_214336.000045</t>
+  </si>
+  <si>
+    <t>Data_20180120_214336</t>
+  </si>
+  <si>
+    <t>Data_20180120_214336.000046</t>
+  </si>
+  <si>
+    <t>Data_20180120_214336.000047</t>
+  </si>
+  <si>
+    <t>Data_20180120_214336.000048</t>
+  </si>
+  <si>
+    <t>Data_20180120_214336.000049</t>
+  </si>
+  <si>
+    <t>Data_20180120_214336.000050</t>
+  </si>
+  <si>
+    <t>Data_20180120_214336.000051</t>
+  </si>
+  <si>
+    <t>Data_20180120_214336.000052</t>
+  </si>
+  <si>
+    <t>Data_20180120_214336.000053</t>
+  </si>
+  <si>
+    <t>Data_20180120_214336.000054</t>
+  </si>
+  <si>
+    <t>Data_20180120_214336.000055</t>
+  </si>
+  <si>
+    <t>Data_20180120_214336.000056</t>
+  </si>
+  <si>
+    <t>Data_20180120_214336.000057</t>
+  </si>
+  <si>
+    <t>Data_20180120_214336.000058</t>
+  </si>
+  <si>
+    <t>Data_20180120_214336.000059</t>
+  </si>
+  <si>
+    <t>Data_20180120_214336.000060</t>
   </si>
 </sst>
 </file>
@@ -462,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q16"/>
+  <dimension ref="A1:Q17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:17">
@@ -523,52 +526,52 @@
         <v>17</v>
       </c>
       <c r="B2" s="1" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C2" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D2" t="n">
-        <v>-4.229400398706723</v>
+        <v>13.40670788674395</v>
       </c>
       <c r="E2" t="n">
-        <v>12.59799188807671</v>
+        <v>-14.99279412501885</v>
       </c>
       <c r="F2" t="s">
         <v>18</v>
       </c>
       <c r="G2" t="n">
-        <v>13.01920971413401</v>
+        <v>20.87611215041883</v>
       </c>
       <c r="H2" t="n">
-        <v>11.56006161295454</v>
+        <v>13.46707513725511</v>
       </c>
       <c r="I2" t="n">
-        <v>1.459148101179469</v>
+        <v>7.409037013163722</v>
       </c>
       <c r="J2" t="n">
-        <v>-1.606865949165527e-08</v>
+        <v>7.757136127105784</v>
       </c>
       <c r="K2" t="n">
-        <v>11.56006159688588</v>
+        <v>21.22421126436089</v>
       </c>
       <c r="L2" t="n">
-        <v>3.933822174127514</v>
+        <v>30.88311856411082</v>
       </c>
       <c r="M2" t="n">
-        <v>1.020723723023195e-07</v>
+        <v>29.90732835156448</v>
       </c>
       <c r="N2" t="n">
-        <v>1.383318451573712</v>
+        <v>1.081317341304978</v>
       </c>
       <c r="O2" t="b">
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5867740283782682</v>
+        <v>-0.06047442678459584</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.972765389433759</v>
+        <v>-0.0613850957706193</v>
       </c>
     </row>
     <row r="3" spans="1:17">
@@ -576,52 +579,52 @@
         <v>19</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C3" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D3" t="n">
-        <v>-7.585525158281533</v>
+        <v>-14.00971066585028</v>
       </c>
       <c r="E3" t="n">
-        <v>-11.14638854582135</v>
+        <v>11.15981194326068</v>
       </c>
       <c r="F3" t="s">
         <v>18</v>
       </c>
       <c r="G3" t="n">
-        <v>13.94611407327717</v>
+        <v>16.96203679381361</v>
       </c>
       <c r="H3" t="n">
-        <v>12.20630841657322</v>
+        <v>22.47520076612922</v>
       </c>
       <c r="I3" t="n">
-        <v>1.739805656703949</v>
+        <v>-5.51316397231561</v>
       </c>
       <c r="J3" t="n">
-        <v>4.593453054592234e-09</v>
+        <v>-4.639864195940445</v>
       </c>
       <c r="K3" t="n">
-        <v>12.20630842116667</v>
+        <v>17.83533657018877</v>
       </c>
       <c r="L3" t="n">
-        <v>3.933822174127514</v>
+        <v>47.97994588705669</v>
       </c>
       <c r="M3" t="n">
-        <v>1.020723719669408e-07</v>
+        <v>47.00415567451035</v>
       </c>
       <c r="N3" t="n">
-        <v>1.123440206228027</v>
+        <v>0.4000582808140068</v>
       </c>
       <c r="O3" t="b">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0.699636150036272</v>
+        <v>-0.1232202239569194</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.159870408431281</v>
+        <v>-0.1244348159006706</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -629,52 +632,52 @@
         <v>20</v>
       </c>
       <c r="B4" s="1" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C4" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D4" t="n">
-        <v>6.936342233167339</v>
+        <v>15.16249921079143</v>
       </c>
       <c r="E4" t="n">
-        <v>30.45356584416535</v>
+        <v>1.258268026653411</v>
       </c>
       <c r="F4" t="s">
         <v>18</v>
       </c>
       <c r="G4" t="n">
-        <v>30.50067662057578</v>
+        <v>14.12866311998771</v>
       </c>
       <c r="H4" t="n">
-        <v>31.09906353441829</v>
+        <v>12.89018035448961</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5983869138425106</v>
+        <v>1.238482765498098</v>
       </c>
       <c r="J4" t="n">
-        <v>-4.748733498263497e-08</v>
+        <v>1.719314124621234</v>
       </c>
       <c r="K4" t="n">
-        <v>31.09906348693096</v>
+        <v>14.60949447911084</v>
       </c>
       <c r="L4" t="n">
-        <v>3.933822174127527</v>
+        <v>36.71619339597766</v>
       </c>
       <c r="M4" t="n">
-        <v>1.02072385185016e-07</v>
+        <v>35.74040318343133</v>
       </c>
       <c r="N4" t="n">
-        <v>6.473991381464103</v>
+        <v>0.06255804777299094</v>
       </c>
       <c r="O4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.2406320975570746</v>
+        <v>-0.07702803040092079</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.3989245685214089</v>
+        <v>-0.07801099777632131</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -682,52 +685,52 @@
         <v>21</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C5" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D5" t="n">
-        <v>-27.36270515855208</v>
+        <v>6.784765156997452</v>
       </c>
       <c r="E5" t="n">
-        <v>3.820391673025171</v>
+        <v>-12.30541047963035</v>
       </c>
       <c r="F5" t="s">
         <v>18</v>
       </c>
       <c r="G5" t="n">
-        <v>25.30611127848498</v>
+        <v>12.90843847975439</v>
       </c>
       <c r="H5" t="n">
-        <v>30.326175094186</v>
+        <v>15.64282584307156</v>
       </c>
       <c r="I5" t="n">
-        <v>-5.020063815701018</v>
+        <v>-2.734387363317166</v>
       </c>
       <c r="J5" t="n">
-        <v>2.841505215148759e-08</v>
+        <v>-1.403584814600667</v>
       </c>
       <c r="K5" t="n">
-        <v>30.32617512260105</v>
+        <v>14.23924102847089</v>
       </c>
       <c r="L5" t="n">
-        <v>3.933822174127546</v>
+        <v>35.65205898777293</v>
       </c>
       <c r="M5" t="n">
-        <v>1.020724043898662e-07</v>
+        <v>34.67626877522659</v>
       </c>
       <c r="N5" t="n">
-        <v>6.163186183784885</v>
+        <v>0.1235707495610542</v>
       </c>
       <c r="O5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-2.018741654605559</v>
+        <v>-0.2161634297024739</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.346709153498125</v>
+        <v>-0.2190009056002166</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -735,52 +738,52 @@
         <v>22</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C6" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D6" t="n">
-        <v>12.21262988442415</v>
+        <v>-10.9067014991214</v>
       </c>
       <c r="E6" t="n">
-        <v>14.33645310392244</v>
+        <v>-16.66477593045312</v>
       </c>
       <c r="F6" t="s">
         <v>18</v>
       </c>
       <c r="G6" t="n">
-        <v>17.8705885412703</v>
+        <v>19.75357263784946</v>
       </c>
       <c r="H6" t="n">
-        <v>15.91254321909321</v>
+        <v>21.45565489262939</v>
       </c>
       <c r="I6" t="n">
-        <v>1.958045322177092</v>
+        <v>-1.702082254779928</v>
       </c>
       <c r="J6" t="n">
-        <v>-3.809754194518729e-08</v>
+        <v>-2.003517927562958</v>
       </c>
       <c r="K6" t="n">
-        <v>15.91254318099567</v>
+        <v>19.45213696506643</v>
       </c>
       <c r="L6" t="n">
-        <v>3.933822174127525</v>
+        <v>38.54281863295891</v>
       </c>
       <c r="M6" t="n">
-        <v>1.020723836293899e-07</v>
+        <v>37.56702842041258</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3669652395479821</v>
+        <v>0.6970704284320665</v>
       </c>
       <c r="O6" t="b">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7873979003327921</v>
+        <v>0.04719573885985311</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.305363543907185</v>
+        <v>0.04777054809019966</v>
       </c>
     </row>
     <row r="7" spans="1:17">
@@ -788,52 +791,52 @@
         <v>23</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C7" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.039800158258757</v>
+        <v>3.446138076042281</v>
       </c>
       <c r="E7" t="n">
-        <v>11.3299682663736</v>
+        <v>17.82218324159382</v>
       </c>
       <c r="F7" t="s">
         <v>18</v>
       </c>
       <c r="G7" t="n">
-        <v>10.53955641694504</v>
+        <v>19.45058073659986</v>
       </c>
       <c r="H7" t="n">
-        <v>10.50607300553116</v>
+        <v>16.73978794683838</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03348341141387579</v>
+        <v>2.710792789761484</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.281073781467178e-08</v>
+        <v>-0.05093711871005923</v>
       </c>
       <c r="K7" t="n">
-        <v>10.50607298272043</v>
+        <v>16.68885082812832</v>
       </c>
       <c r="L7" t="n">
-        <v>3.933822174127514</v>
+        <v>38.41274569994832</v>
       </c>
       <c r="M7" t="n">
-        <v>1.020723722956527e-07</v>
+        <v>37.43695548740199</v>
       </c>
       <c r="N7" t="n">
-        <v>1.807163801945037</v>
+        <v>0.2648457089816371</v>
       </c>
       <c r="O7" t="b">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01346484935399776</v>
+        <v>0.4330946839369786</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0223222889767451</v>
+        <v>0.4383866407909792</v>
       </c>
     </row>
     <row r="8" spans="1:17">
@@ -841,52 +844,52 @@
         <v>24</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D8" t="n">
-        <v>-22.38024991159007</v>
+        <v>-45.05916476162898</v>
       </c>
       <c r="E8" t="n">
-        <v>-8.290482612828129</v>
+        <v>-7.475009989108345</v>
       </c>
       <c r="F8" t="s">
         <v>18</v>
       </c>
       <c r="G8" t="n">
-        <v>24.21779708941035</v>
+        <v>49.17818545130499</v>
       </c>
       <c r="H8" t="n">
-        <v>24.21197113881453</v>
+        <v>32.67702135280349</v>
       </c>
       <c r="I8" t="n">
-        <v>0.00582595059581692</v>
+        <v>16.5011640985015</v>
       </c>
       <c r="J8" t="n">
-        <v>4.096687647249113e-08</v>
+        <v>13.89432104550924</v>
       </c>
       <c r="K8" t="n">
-        <v>24.21197117978141</v>
+        <v>46.57134239831274</v>
       </c>
       <c r="L8" t="n">
-        <v>3.933822174127535</v>
+        <v>45.49970028245694</v>
       </c>
       <c r="M8" t="n">
-        <v>1.020723928693991e-07</v>
+        <v>44.5239100699106</v>
       </c>
       <c r="N8" t="n">
-        <v>3.704452875324964</v>
+        <v>4.568858661827145</v>
       </c>
       <c r="O8" t="b">
         <v>1</v>
       </c>
       <c r="P8" t="n">
-        <v>0.002342800173286983</v>
+        <v>0.3772502705910946</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.003883939664527573</v>
+        <v>0.3811650276562406</v>
       </c>
     </row>
     <row r="9" spans="1:17">
@@ -894,52 +897,52 @@
         <v>25</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D9" t="n">
-        <v>-14.7553421001751</v>
+        <v>15.00925938994981</v>
       </c>
       <c r="E9" t="n">
-        <v>21.73706300018365</v>
+        <v>-12.95907801847386</v>
       </c>
       <c r="F9" t="s">
         <v>18</v>
       </c>
       <c r="G9" t="n">
-        <v>27.71241254236175</v>
+        <v>20.15261257609242</v>
       </c>
       <c r="H9" t="n">
-        <v>25.7639143853562</v>
+        <v>12.94052987606696</v>
       </c>
       <c r="I9" t="n">
-        <v>1.948498157005549</v>
+        <v>7.212082700025459</v>
       </c>
       <c r="J9" t="n">
-        <v>3.650826370083708e-08</v>
+        <v>7.795875790486689</v>
       </c>
       <c r="K9" t="n">
-        <v>25.76391442186447</v>
+        <v>20.73640566655365</v>
       </c>
       <c r="L9" t="n">
-        <v>3.933822174127522</v>
+        <v>31.22010230359146</v>
       </c>
       <c r="M9" t="n">
-        <v>1.020723808329485e-07</v>
+        <v>30.24431209104512</v>
       </c>
       <c r="N9" t="n">
-        <v>4.328543039446838</v>
+        <v>0.9915425053476425</v>
       </c>
       <c r="O9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>0.7835586243348122</v>
+        <v>-0.1009091227448599</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.298998717533325</v>
+        <v>-0.102413044498889</v>
       </c>
     </row>
     <row r="10" spans="1:17">
@@ -947,52 +950,52 @@
         <v>26</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D10" t="n">
-        <v>14.09060319255523</v>
+        <v>-20.61340418437623</v>
       </c>
       <c r="E10" t="n">
-        <v>8.945564849255105</v>
+        <v>-3.952818610654547</v>
       </c>
       <c r="F10" t="s">
         <v>18</v>
       </c>
       <c r="G10" t="n">
-        <v>17.92754175575471</v>
+        <v>22.46385054205804</v>
       </c>
       <c r="H10" t="n">
-        <v>14.24639036530311</v>
+        <v>24.64495538653476</v>
       </c>
       <c r="I10" t="n">
-        <v>3.681151390451596</v>
+        <v>-2.181104844476717</v>
       </c>
       <c r="J10" t="n">
-        <v>-3.116574066839883e-08</v>
+        <v>-3.865588174741718</v>
       </c>
       <c r="K10" t="n">
-        <v>14.24639033413737</v>
+        <v>20.77936721179304</v>
       </c>
       <c r="L10" t="n">
-        <v>3.933822174127526</v>
+        <v>49.61705112760723</v>
       </c>
       <c r="M10" t="n">
-        <v>1.020723843209679e-07</v>
+        <v>48.64126091506089</v>
       </c>
       <c r="N10" t="n">
-        <v>0.3030525648739315</v>
+        <v>0.8024805427992955</v>
       </c>
       <c r="O10" t="b">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.480318566155187</v>
+        <v>0.2338950005545743</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.45410089207913</v>
+        <v>0.2361267077192802</v>
       </c>
     </row>
     <row r="11" spans="1:17">
@@ -1000,52 +1003,52 @@
         <v>27</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C11" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.06715556140871</v>
+        <v>-17.42747920145536</v>
       </c>
       <c r="E11" t="n">
-        <v>18.08121041562056</v>
+        <v>-13.20641729571971</v>
       </c>
       <c r="F11" t="s">
         <v>18</v>
       </c>
       <c r="G11" t="n">
-        <v>19.85064731528694</v>
+        <v>22.42370185011604</v>
       </c>
       <c r="H11" t="n">
-        <v>16.38898631145719</v>
+        <v>23.59816612646912</v>
       </c>
       <c r="I11" t="n">
-        <v>3.46166100382975</v>
+        <v>-1.174464276353085</v>
       </c>
       <c r="J11" t="n">
-        <v>-5.234419406425958e-09</v>
+        <v>-2.547669098749047</v>
       </c>
       <c r="K11" t="n">
-        <v>16.38898630622277</v>
+        <v>21.05049702772008</v>
       </c>
       <c r="L11" t="n">
-        <v>3.933822174127516</v>
+        <v>43.00509517489046</v>
       </c>
       <c r="M11" t="n">
-        <v>1.02072373665625e-07</v>
+        <v>42.02930496234411</v>
       </c>
       <c r="N11" t="n">
-        <v>0.5585595325316726</v>
+        <v>0.8994091689598209</v>
       </c>
       <c r="O11" t="b">
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.392053864277546</v>
+        <v>0.2041275291045248</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.307773953696121</v>
+        <v>0.2063644680206731</v>
       </c>
     </row>
     <row r="12" spans="1:17">
@@ -1053,52 +1056,52 @@
         <v>28</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C12" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D12" t="n">
-        <v>14.28903032719646</v>
+        <v>-36.8123455676492</v>
       </c>
       <c r="E12" t="n">
-        <v>-20.46054638787901</v>
+        <v>-6.706612715598907</v>
       </c>
       <c r="F12" t="s">
         <v>18</v>
       </c>
       <c r="G12" t="n">
-        <v>24.28244070015385</v>
+        <v>35.7072751906645</v>
       </c>
       <c r="H12" t="n">
-        <v>23.68023017063854</v>
+        <v>29.96739014420967</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6022105295153111</v>
+        <v>5.73988504645483</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.847280959715621e-08</v>
+        <v>8.471933171313717</v>
       </c>
       <c r="K12" t="n">
-        <v>23.68023014216573</v>
+        <v>38.43932331552338</v>
       </c>
       <c r="L12" t="n">
-        <v>3.933822174127526</v>
+        <v>47.23934403015073</v>
       </c>
       <c r="M12" t="n">
-        <v>1.020723847240769e-07</v>
+        <v>46.26355381760438</v>
       </c>
       <c r="N12" t="n">
-        <v>3.490621375282168</v>
+        <v>3.331878997467717</v>
       </c>
       <c r="O12" t="b">
         <v>1</v>
       </c>
       <c r="P12" t="n">
-        <v>0.2421697364822928</v>
+        <v>-0.3883582151563115</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.4014736962188845</v>
+        <v>-0.3922444436775328</v>
       </c>
     </row>
     <row r="13" spans="1:17">
@@ -1106,52 +1109,52 @@
         <v>29</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C13" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>10.40118487897376</v>
+        <v>-7.131880906351434</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.490369908150996</v>
+        <v>-17.41674614004691</v>
       </c>
       <c r="F13" t="s">
         <v>18</v>
       </c>
       <c r="G13" t="n">
-        <v>12.74085632351055</v>
+        <v>18.75118529339538</v>
       </c>
       <c r="H13" t="n">
-        <v>10.49932625987924</v>
+        <v>20.21537407108804</v>
       </c>
       <c r="I13" t="n">
-        <v>2.241530063631311</v>
+        <v>-1.464188777692662</v>
       </c>
       <c r="J13" t="n">
-        <v>-4.366677974864336e-08</v>
+        <v>-1.518826795364542</v>
       </c>
       <c r="K13" t="n">
-        <v>10.49932621621246</v>
+        <v>18.6965472757235</v>
       </c>
       <c r="L13" t="n">
-        <v>3.933822174127521</v>
+        <v>36.80896796365115</v>
       </c>
       <c r="M13" t="n">
-        <v>1.020723791063225e-07</v>
+        <v>35.83317775110481</v>
       </c>
       <c r="N13" t="n">
-        <v>1.809876910583982</v>
+        <v>0.5914743053122052</v>
       </c>
       <c r="O13" t="b">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9013969419848895</v>
+        <v>0.008742478084440671</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.494353370969349</v>
+        <v>0.008853772212560701</v>
       </c>
     </row>
     <row r="14" spans="1:17">
@@ -1159,52 +1162,52 @@
         <v>30</v>
       </c>
       <c r="B14" s="1" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.763308357209354</v>
+        <v>10.06025483969785</v>
       </c>
       <c r="E14" t="n">
-        <v>7.087722916941972</v>
+        <v>-5.652195049787607</v>
       </c>
       <c r="F14" t="s">
         <v>18</v>
       </c>
       <c r="G14" t="n">
-        <v>8.315943902467318</v>
+        <v>9.951076787608987</v>
       </c>
       <c r="H14" t="n">
-        <v>8.355542835776816</v>
+        <v>14.56660859386217</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.03959893330949882</v>
+        <v>-4.615531806253184</v>
       </c>
       <c r="J14" t="n">
-        <v>-2.954971342310909e-08</v>
+        <v>-2.736946732966584</v>
       </c>
       <c r="K14" t="n">
-        <v>8.355542806227103</v>
+        <v>11.82966186089559</v>
       </c>
       <c r="L14" t="n">
-        <v>3.933822174127514</v>
+        <v>38.00328553975786</v>
       </c>
       <c r="M14" t="n">
-        <v>1.02072371944023e-07</v>
+        <v>37.02749532721153</v>
       </c>
       <c r="N14" t="n">
-        <v>2.671966517922796</v>
+        <v>0.4996949015342521</v>
       </c>
       <c r="O14" t="b">
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.01592409160100447</v>
+        <v>-0.2960944044551798</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.02639926857438204</v>
+        <v>-0.2997498499834243</v>
       </c>
     </row>
     <row r="15" spans="1:17">
@@ -1212,52 +1215,52 @@
         <v>31</v>
       </c>
       <c r="B15" s="1" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>0.318304742319043</v>
+        <v>-14.41257040345503</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.198897941952368</v>
+        <v>3.904602971927446</v>
       </c>
       <c r="F15" t="s">
         <v>18</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4583320779332982</v>
+        <v>14.42204514154366</v>
       </c>
       <c r="H15" t="n">
-        <v>7.17886772251444</v>
+        <v>22.60756711150716</v>
       </c>
       <c r="I15" t="n">
-        <v>-6.720535644581141</v>
+        <v>-8.185521969963499</v>
       </c>
       <c r="J15" t="n">
-        <v>-3.863229808747086e-08</v>
+        <v>-7.156104409018047</v>
       </c>
       <c r="K15" t="n">
-        <v>7.178867683882141</v>
+        <v>15.45146270248911</v>
       </c>
       <c r="L15" t="n">
-        <v>3.933822174127514</v>
+        <v>50.11188076285468</v>
       </c>
       <c r="M15" t="n">
-        <v>1.020723721440128e-07</v>
+        <v>49.13609055030835</v>
       </c>
       <c r="N15" t="n">
-        <v>3.14514836524134</v>
+        <v>0.06238989550968807</v>
       </c>
       <c r="O15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>-2.702560284146675</v>
+        <v>-0.1422603765695876</v>
       </c>
       <c r="Q15" t="n">
-        <v>-4.480356969005749</v>
+        <v>-0.1436047428803733</v>
       </c>
     </row>
     <row r="16" spans="1:17">
@@ -1265,52 +1268,105 @@
         <v>32</v>
       </c>
       <c r="B16" s="1" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D16" t="n">
-        <v>-8.177937969688578</v>
+        <v>0.1693416123353302</v>
       </c>
       <c r="E16" t="n">
-        <v>-21.85798934431147</v>
+        <v>-11.66904160227692</v>
       </c>
       <c r="F16" t="s">
         <v>18</v>
       </c>
       <c r="G16" t="n">
-        <v>23.56727048122157</v>
+        <v>12.89977720812707</v>
       </c>
       <c r="H16" t="n">
-        <v>21.52751171232399</v>
+        <v>17.81643456093559</v>
       </c>
       <c r="I16" t="n">
-        <v>2.039758768897585</v>
+        <v>-4.916657352808521</v>
       </c>
       <c r="J16" t="n">
-        <v>8.105074131498886e-09</v>
+        <v>-5.54802598127823</v>
       </c>
       <c r="K16" t="n">
-        <v>21.52751172042906</v>
+        <v>12.26840857965736</v>
       </c>
       <c r="L16" t="n">
-        <v>3.933822174127517</v>
+        <v>39.16644296436474</v>
       </c>
       <c r="M16" t="n">
-        <v>1.020723751373223e-07</v>
+        <v>38.1906527518184</v>
       </c>
       <c r="N16" t="n">
-        <v>2.624938690052942</v>
+        <v>0.4244527400422523</v>
       </c>
       <c r="O16" t="b">
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>0.8202576906635963</v>
+        <v>0.09810623299478351</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.359839143016782</v>
+        <v>0.09928277796216782</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17">
+      <c r="A17" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="C17" t="n">
+        <v>60</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3.53900805282754</v>
+      </c>
+      <c r="E17" t="n">
+        <v>9.264692622068909</v>
+      </c>
+      <c r="F17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G17" t="n">
+        <v>9.153096005733651</v>
+      </c>
+      <c r="H17" t="n">
+        <v>16.70927395331922</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-7.556177947585571</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-6.094304780345157</v>
+      </c>
+      <c r="K17" t="n">
+        <v>10.61496917297407</v>
+      </c>
+      <c r="L17" t="n">
+        <v>42.45087043920582</v>
+      </c>
+      <c r="M17" t="n">
+        <v>41.47508022665949</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.6558653099853271</v>
+      </c>
+      <c r="O17" t="b">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>-0.2186511191853237</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>-0.2210774197497092</v>
       </c>
     </row>
   </sheetData>
